--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_1334_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_1334_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6a2c71bcdad94e73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd75ae93b3a8649ea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,156 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.8100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     18.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.3900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>13/08/2026</x:t>
         </x:is>
       </x:c>

--- a/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_1334_completo.xlsx
+++ b/138_Cuenca_Chira/_raw_reportes_xlsx/IDConfig_1334_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd75ae93b3a8649ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rfc0583a6ada843e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,666 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.0800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.0000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.6200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.5800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     23.7600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.9100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.2000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     21.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.4000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.7400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.4900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.8900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.9900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.2700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     20.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.1700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     19.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.7100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
